--- a/Data/Excel/world_crop.xlsx
+++ b/Data/Excel/world_crop.xlsx
@@ -242,7 +242,7 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>1</v>
+        <v>30500001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -250,13 +250,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>5000301</v>
+        <v>20200001</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>20100001</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -280,7 +280,7 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>2</v>
+        <v>30500002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -288,13 +288,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>5000301</v>
+        <v>20200002</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>20100002</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -318,7 +318,7 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>3</v>
+        <v>30500003</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -326,13 +326,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>5000301</v>
+        <v>20200003</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>20100003</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -356,7 +356,7 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>4</v>
+        <v>30500004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -364,13 +364,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>5000301</v>
+        <v>20200004</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>20100004</v>
       </c>
       <c r="G8">
         <v>14</v>
